--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,123 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125686095</v>
+      </c>
+      <c r="B3" t="n">
+        <v>108372</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>231645</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Växeltandsfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hieracium dentifolium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(C. G. Westerl.) Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skinnarsbovägen, 125 m SSO vägskälet till Sandsjö, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>546014</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6419826</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>grusvägdike mot blandskog</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>AS25231</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108372</v>
+        <v>108373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108373</v>
+        <v>108378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108378</v>
+        <v>108382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108382</v>
+        <v>108384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108384</v>
+        <v>108394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108394</v>
+        <v>108398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108398</v>
+        <v>108401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108401</v>
+        <v>108402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108402</v>
+        <v>108419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108777</v>
+        <v>108780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125686095</v>
       </c>
       <c r="B3" t="n">
-        <v>108780</v>
+        <v>108788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17342165</v>
+        <v>98327164</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>101246</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horns socken, Åbyboda, Ög</t>
+          <t>Åbyboda Sandsjö, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546080.5203263053</v>
+        <v>545938</v>
       </c>
       <c r="R2" t="n">
-        <v>6419779.745050629</v>
+        <v>6419940</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1963-05-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1963-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>f. fl. alba</t>
+          <t>Ekoxeuppropet 2020. Frikrypande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,78 +776,67 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>lövskog</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Anders Svenson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125686095</v>
+        <v>17342165</v>
       </c>
       <c r="B3" t="n">
-        <v>108788</v>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>231645</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Växeltandsfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hieracium dentifolium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(C. G. Westerl.) Johanss. &amp; Sam.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skinnarsbovägen, 125 m SSO vägskälet till Sandsjö, Ög</t>
+          <t>Horns socken, Åbyboda, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546014</v>
+        <v>546081</v>
       </c>
       <c r="R3" t="n">
-        <v>6419826</v>
+        <v>6419780</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>1963-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>1963-05-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>f. fl. alba</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,25 +879,20 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>grusvägdike mot blandskog</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Oskarshamn-Herbarium OHN</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>AS25231, OHN 319156</t>
-        </is>
-      </c>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -917,6 +905,551 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>82562018</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åbyboda, Skinnarsbovägen vid bäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546011</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6419826</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>brantsluttande hassellund</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>82913222</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åbyboda, Sandsjö, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545950</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6419941</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-03-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-03-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>ek-hassellund, vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106010604</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sandsjö, vid infarten, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545933</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6419941</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>grusvägkant mot hasseldunge</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125686098</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skinnarsbovägen, vid brotrumman, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546069</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6419733</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>bryn mot hassellund</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Oskarshamn-Herbarium OHN</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>AS25228, OHN 319234</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125686095</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108883</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>231645</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Växeltandsfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hieracium dentifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(C. G. Westerl.) Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skinnarsbovägen, 125 m SSO vägskälet till Sandsjö, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>546014</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6419826</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>grusvägdike mot blandskog</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Oskarshamn-Herbarium OHN</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>AS25231, OHN 319156</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53708-2025 artfynd.xlsx
+++ b/artfynd/A 53708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98327164</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17342165</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82562018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82913222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106010604</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125686098</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,8 +1485,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125686095</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>